--- a/data/outputs/sector_summary.xlsx
+++ b/data/outputs/sector_summary.xlsx
@@ -462,7 +462,7 @@
         <v>27615980.29119994</v>
       </c>
       <c r="D2">
-        <v>152523.1181706927</v>
+        <v>148883.5101809135</v>
       </c>
       <c r="E2">
         <v>0.005786475883708949</v>
@@ -477,7 +477,7 @@
         <v>0.2451393949802069</v>
       </c>
       <c r="I2">
-        <v>0.005523002137255126</v>
+        <v>0.005391208590497017</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -491,7 +491,7 @@
         <v>17742449.14435855</v>
       </c>
       <c r="D3">
-        <v>98305.66385668603</v>
+        <v>95963.44596080088</v>
       </c>
       <c r="E3">
         <v>0.005350834438460387</v>
@@ -506,7 +506,7 @@
         <v>0.1574947984048608</v>
       </c>
       <c r="I3">
-        <v>0.005540704276891988</v>
+        <v>0.005408692181108138</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -520,7 +520,7 @@
         <v>16544740.35864704</v>
       </c>
       <c r="D4">
-        <v>83636.47337916671</v>
+        <v>81638.20659304732</v>
       </c>
       <c r="E4">
         <v>0.005109577392926078</v>
@@ -535,7 +535,7 @@
         <v>0.1468630698188813</v>
       </c>
       <c r="I4">
-        <v>0.005055169894851473</v>
+        <v>0.004934390315190376</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -549,7 +549,7 @@
         <v>13487831.27748725</v>
       </c>
       <c r="D5">
-        <v>70034.54270499259</v>
+        <v>68361.82342576774</v>
       </c>
       <c r="E5">
         <v>0.005108022258887793</v>
@@ -564,7 +564,7 @@
         <v>0.1197277360460728</v>
       </c>
       <c r="I5">
-        <v>0.005192424287060022</v>
+        <v>0.005068407368045264</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -578,7 +578,7 @@
         <v>13361890.28490731</v>
       </c>
       <c r="D6">
-        <v>141562.6242394228</v>
+        <v>138201.7092190425</v>
       </c>
       <c r="E6">
         <v>0.009020761208613131</v>
@@ -593,7 +593,7 @@
         <v>0.1186097927973194</v>
       </c>
       <c r="I6">
-        <v>0.01059450580875689</v>
+        <v>0.01034297590178134</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -607,7 +607,7 @@
         <v>12753198.85762022</v>
       </c>
       <c r="D7">
-        <v>122284.9546254614</v>
+        <v>119373.1685739635</v>
       </c>
       <c r="E7">
         <v>0.008200570620167135</v>
@@ -619,10 +619,10 @@
         <v>1.560674157303371</v>
       </c>
       <c r="H7">
-        <v>0.1132066078789718</v>
+        <v>0.1132066078789719</v>
       </c>
       <c r="I7">
-        <v>0.009588571149143056</v>
+        <v>0.009360253055462729</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -636,7 +636,7 @@
         <v>11148101.06103239</v>
       </c>
       <c r="D8">
-        <v>20921.60484600998</v>
+        <v>20420.85603718308</v>
       </c>
       <c r="E8">
         <v>0.002118934499878127</v>
@@ -651,7 +651,7 @@
         <v>0.09895860007368718</v>
       </c>
       <c r="I8">
-        <v>0.001876696733503822</v>
+        <v>0.001831778876544556</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/sector_summary.xlsx
+++ b/data/outputs/sector_summary.xlsx
@@ -459,25 +459,25 @@
         <v>1972</v>
       </c>
       <c r="C2">
-        <v>27615980.29119994</v>
+        <v>27612128.92570351</v>
       </c>
       <c r="D2">
-        <v>148883.5101809135</v>
+        <v>46690.29756361964</v>
       </c>
       <c r="E2">
-        <v>0.005786475883708949</v>
+        <v>0.001713220526860417</v>
       </c>
       <c r="F2">
-        <v>0.6895968543224502</v>
+        <v>0.6893616691836554</v>
       </c>
       <c r="G2">
-        <v>1.342292089249493</v>
+        <v>1.269269776876268</v>
       </c>
       <c r="H2">
-        <v>0.2451393949802069</v>
+        <v>0.2451310518128871</v>
       </c>
       <c r="I2">
-        <v>0.005391208590497017</v>
+        <v>0.001690934360376562</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -488,25 +488,25 @@
         <v>1271</v>
       </c>
       <c r="C3">
-        <v>17742449.14435855</v>
+        <v>17738299.12155825</v>
       </c>
       <c r="D3">
-        <v>95963.44596080088</v>
+        <v>94367.40951191922</v>
       </c>
       <c r="E3">
-        <v>0.005350834438460387</v>
+        <v>0.004872875091881172</v>
       </c>
       <c r="F3">
-        <v>0.6897019629952355</v>
+        <v>0.6900363533654161</v>
       </c>
       <c r="G3">
-        <v>1.313139260424862</v>
+        <v>1.280881195908733</v>
       </c>
       <c r="H3">
-        <v>0.1574947984048608</v>
+        <v>0.1574745624554699</v>
       </c>
       <c r="I3">
-        <v>0.005408692181108138</v>
+        <v>0.005319980730127036</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -517,25 +517,25 @@
         <v>1139</v>
       </c>
       <c r="C4">
-        <v>16544740.35864704</v>
+        <v>16544460.35796101</v>
       </c>
       <c r="D4">
-        <v>81638.20659304732</v>
+        <v>59192.10363793441</v>
       </c>
       <c r="E4">
-        <v>0.005109577392926078</v>
+        <v>0.003794104472979617</v>
       </c>
       <c r="F4">
-        <v>0.6873676359846619</v>
+        <v>0.687074752583591</v>
       </c>
       <c r="G4">
-        <v>1.377524143985953</v>
+        <v>1.287093942054434</v>
       </c>
       <c r="H4">
-        <v>0.1468630698188813</v>
+        <v>0.1468760695756554</v>
       </c>
       <c r="I4">
-        <v>0.004934390315190376</v>
+        <v>0.003577759706707618</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -546,25 +546,25 @@
         <v>976</v>
       </c>
       <c r="C5">
-        <v>13487831.27748725</v>
+        <v>13488381.37391186</v>
       </c>
       <c r="D5">
-        <v>68361.82342576774</v>
+        <v>94422.09484959475</v>
       </c>
       <c r="E5">
-        <v>0.005108022258887793</v>
+        <v>0.006232861936331147</v>
       </c>
       <c r="F5">
-        <v>0.6898398724708215</v>
+        <v>0.6905296766388008</v>
       </c>
       <c r="G5">
-        <v>1.360655737704918</v>
+        <v>1.450819672131147</v>
       </c>
       <c r="H5">
-        <v>0.1197277360460728</v>
+        <v>0.1197452439229522</v>
       </c>
       <c r="I5">
-        <v>0.005068407368045264</v>
+        <v>0.007000253939454762</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -575,25 +575,25 @@
         <v>943</v>
       </c>
       <c r="C6">
-        <v>13361890.28490731</v>
+        <v>13359135.74845482</v>
       </c>
       <c r="D6">
-        <v>138201.7092190425</v>
+        <v>49329.10970550036</v>
       </c>
       <c r="E6">
-        <v>0.009020761208613131</v>
+        <v>0.003953842396188018</v>
       </c>
       <c r="F6">
-        <v>0.6909876265486031</v>
+        <v>0.6922683380702455</v>
       </c>
       <c r="G6">
-        <v>1.542948038176034</v>
+        <v>1.250265111346766</v>
       </c>
       <c r="H6">
-        <v>0.1186097927973194</v>
+        <v>0.1185978453940032</v>
       </c>
       <c r="I6">
-        <v>0.01034297590178134</v>
+        <v>0.003692537499007449</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -604,25 +604,25 @@
         <v>890</v>
       </c>
       <c r="C7">
-        <v>12753198.85762022</v>
+        <v>12752907.34577825</v>
       </c>
       <c r="D7">
-        <v>119373.1685739635</v>
+        <v>34882.611540844</v>
       </c>
       <c r="E7">
-        <v>0.008200570620167135</v>
+        <v>0.003022402970105342</v>
       </c>
       <c r="F7">
-        <v>0.6916452876859672</v>
+        <v>0.6909440643754788</v>
       </c>
       <c r="G7">
-        <v>1.560674157303371</v>
+        <v>1.265168539325843</v>
       </c>
       <c r="H7">
-        <v>0.1132066078789719</v>
+        <v>0.1132159566455185</v>
       </c>
       <c r="I7">
-        <v>0.009360253055462729</v>
+        <v>0.00273526738609856</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -633,25 +633,25 @@
         <v>809</v>
       </c>
       <c r="C8">
-        <v>11148101.06103239</v>
+        <v>11147001.19290712</v>
       </c>
       <c r="D8">
-        <v>20420.85603718308</v>
+        <v>49601.3950815514</v>
       </c>
       <c r="E8">
-        <v>0.002118934499878127</v>
+        <v>0.004945577544790887</v>
       </c>
       <c r="F8">
-        <v>0.6894714982691714</v>
+        <v>0.6894165745275845</v>
       </c>
       <c r="G8">
-        <v>1.247218788627936</v>
+        <v>1.316440049443758</v>
       </c>
       <c r="H8">
-        <v>0.09895860007368718</v>
+        <v>0.09895927019351372</v>
       </c>
       <c r="I8">
-        <v>0.001831778876544556</v>
+        <v>0.004449752379421378</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/sector_summary.xlsx
+++ b/data/outputs/sector_summary.xlsx
@@ -459,25 +459,25 @@
         <v>1972</v>
       </c>
       <c r="C2">
-        <v>27612128.92570351</v>
+        <v>27615980.29119994</v>
       </c>
       <c r="D2">
-        <v>46690.29756361964</v>
+        <v>148883.5101809135</v>
       </c>
       <c r="E2">
-        <v>0.001713220526860417</v>
+        <v>0.005786475883708949</v>
       </c>
       <c r="F2">
-        <v>0.6893616691836554</v>
+        <v>0.6895968543224502</v>
       </c>
       <c r="G2">
-        <v>1.269269776876268</v>
+        <v>1.342292089249493</v>
       </c>
       <c r="H2">
-        <v>0.2451310518128871</v>
+        <v>0.2451393949802069</v>
       </c>
       <c r="I2">
-        <v>0.001690934360376562</v>
+        <v>0.005391208590497017</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -488,25 +488,25 @@
         <v>1271</v>
       </c>
       <c r="C3">
-        <v>17738299.12155825</v>
+        <v>17742449.14435855</v>
       </c>
       <c r="D3">
-        <v>94367.40951191922</v>
+        <v>95963.44596080088</v>
       </c>
       <c r="E3">
-        <v>0.004872875091881172</v>
+        <v>0.005350834438460387</v>
       </c>
       <c r="F3">
-        <v>0.6900363533654161</v>
+        <v>0.6897019629952355</v>
       </c>
       <c r="G3">
-        <v>1.280881195908733</v>
+        <v>1.313139260424862</v>
       </c>
       <c r="H3">
-        <v>0.1574745624554699</v>
+        <v>0.1574947984048608</v>
       </c>
       <c r="I3">
-        <v>0.005319980730127036</v>
+        <v>0.005408692181108138</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -517,25 +517,25 @@
         <v>1139</v>
       </c>
       <c r="C4">
-        <v>16544460.35796101</v>
+        <v>16544740.35864704</v>
       </c>
       <c r="D4">
-        <v>59192.10363793441</v>
+        <v>81638.20659304732</v>
       </c>
       <c r="E4">
-        <v>0.003794104472979617</v>
+        <v>0.005109577392926078</v>
       </c>
       <c r="F4">
-        <v>0.687074752583591</v>
+        <v>0.6873676359846619</v>
       </c>
       <c r="G4">
-        <v>1.287093942054434</v>
+        <v>1.377524143985953</v>
       </c>
       <c r="H4">
-        <v>0.1468760695756554</v>
+        <v>0.1468630698188813</v>
       </c>
       <c r="I4">
-        <v>0.003577759706707618</v>
+        <v>0.004934390315190376</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -546,25 +546,25 @@
         <v>976</v>
       </c>
       <c r="C5">
-        <v>13488381.37391186</v>
+        <v>13487831.27748725</v>
       </c>
       <c r="D5">
-        <v>94422.09484959475</v>
+        <v>68361.82342576774</v>
       </c>
       <c r="E5">
-        <v>0.006232861936331147</v>
+        <v>0.005108022258887793</v>
       </c>
       <c r="F5">
-        <v>0.6905296766388008</v>
+        <v>0.6898398724708215</v>
       </c>
       <c r="G5">
-        <v>1.450819672131147</v>
+        <v>1.360655737704918</v>
       </c>
       <c r="H5">
-        <v>0.1197452439229522</v>
+        <v>0.1197277360460728</v>
       </c>
       <c r="I5">
-        <v>0.007000253939454762</v>
+        <v>0.005068407368045264</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -575,25 +575,25 @@
         <v>943</v>
       </c>
       <c r="C6">
-        <v>13359135.74845482</v>
+        <v>13361890.28490731</v>
       </c>
       <c r="D6">
-        <v>49329.10970550036</v>
+        <v>138201.7092190425</v>
       </c>
       <c r="E6">
-        <v>0.003953842396188018</v>
+        <v>0.009020761208613131</v>
       </c>
       <c r="F6">
-        <v>0.6922683380702455</v>
+        <v>0.6909876265486031</v>
       </c>
       <c r="G6">
-        <v>1.250265111346766</v>
+        <v>1.542948038176034</v>
       </c>
       <c r="H6">
-        <v>0.1185978453940032</v>
+        <v>0.1186097927973194</v>
       </c>
       <c r="I6">
-        <v>0.003692537499007449</v>
+        <v>0.01034297590178134</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -604,25 +604,25 @@
         <v>890</v>
       </c>
       <c r="C7">
-        <v>12752907.34577825</v>
+        <v>12753198.85762022</v>
       </c>
       <c r="D7">
-        <v>34882.611540844</v>
+        <v>119373.1685739635</v>
       </c>
       <c r="E7">
-        <v>0.003022402970105342</v>
+        <v>0.008200570620167135</v>
       </c>
       <c r="F7">
-        <v>0.6909440643754788</v>
+        <v>0.6916452876859673</v>
       </c>
       <c r="G7">
-        <v>1.265168539325843</v>
+        <v>1.560674157303371</v>
       </c>
       <c r="H7">
-        <v>0.1132159566455185</v>
+        <v>0.1132066078789718</v>
       </c>
       <c r="I7">
-        <v>0.00273526738609856</v>
+        <v>0.009360253055462731</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -633,25 +633,25 @@
         <v>809</v>
       </c>
       <c r="C8">
-        <v>11147001.19290712</v>
+        <v>11148101.06103239</v>
       </c>
       <c r="D8">
-        <v>49601.3950815514</v>
+        <v>20420.85603718308</v>
       </c>
       <c r="E8">
-        <v>0.004945577544790887</v>
+        <v>0.002118934499878127</v>
       </c>
       <c r="F8">
-        <v>0.6894165745275845</v>
+        <v>0.6894714982691714</v>
       </c>
       <c r="G8">
-        <v>1.316440049443758</v>
+        <v>1.247218788627936</v>
       </c>
       <c r="H8">
-        <v>0.09895927019351372</v>
+        <v>0.09895860007368718</v>
       </c>
       <c r="I8">
-        <v>0.004449752379421378</v>
+        <v>0.001831778876544556</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/sector_summary.xlsx
+++ b/data/outputs/sector_summary.xlsx
@@ -459,25 +459,25 @@
         <v>1972</v>
       </c>
       <c r="C2">
-        <v>27615980.29119994</v>
+        <v>27612128.92570351</v>
       </c>
       <c r="D2">
-        <v>148883.5101809135</v>
+        <v>46690.29756361964</v>
       </c>
       <c r="E2">
-        <v>0.005786475883708949</v>
+        <v>0.001713220526860417</v>
       </c>
       <c r="F2">
-        <v>0.6895968543224502</v>
+        <v>0.6893616691836554</v>
       </c>
       <c r="G2">
-        <v>1.342292089249493</v>
+        <v>1.269269776876268</v>
       </c>
       <c r="H2">
-        <v>0.2451393949802069</v>
+        <v>0.2451310518128871</v>
       </c>
       <c r="I2">
-        <v>0.005391208590497017</v>
+        <v>0.001690934360376562</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -488,25 +488,25 @@
         <v>1271</v>
       </c>
       <c r="C3">
-        <v>17742449.14435855</v>
+        <v>17738299.12155825</v>
       </c>
       <c r="D3">
-        <v>95963.44596080088</v>
+        <v>94367.40951191924</v>
       </c>
       <c r="E3">
-        <v>0.005350834438460387</v>
+        <v>0.004872875091881172</v>
       </c>
       <c r="F3">
-        <v>0.6897019629952355</v>
+        <v>0.6900363533654161</v>
       </c>
       <c r="G3">
-        <v>1.313139260424862</v>
+        <v>1.280881195908733</v>
       </c>
       <c r="H3">
-        <v>0.1574947984048608</v>
+        <v>0.1574745624554699</v>
       </c>
       <c r="I3">
-        <v>0.005408692181108138</v>
+        <v>0.005319980730127037</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -517,25 +517,25 @@
         <v>1139</v>
       </c>
       <c r="C4">
-        <v>16544740.35864704</v>
+        <v>16544460.35796101</v>
       </c>
       <c r="D4">
-        <v>81638.20659304732</v>
+        <v>59192.10363793441</v>
       </c>
       <c r="E4">
-        <v>0.005109577392926078</v>
+        <v>0.003794104472979617</v>
       </c>
       <c r="F4">
-        <v>0.6873676359846619</v>
+        <v>0.687074752583591</v>
       </c>
       <c r="G4">
-        <v>1.377524143985953</v>
+        <v>1.287093942054434</v>
       </c>
       <c r="H4">
-        <v>0.1468630698188813</v>
+        <v>0.1468760695756554</v>
       </c>
       <c r="I4">
-        <v>0.004934390315190376</v>
+        <v>0.003577759706707618</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -546,25 +546,25 @@
         <v>976</v>
       </c>
       <c r="C5">
-        <v>13487831.27748725</v>
+        <v>13488381.37391186</v>
       </c>
       <c r="D5">
-        <v>68361.82342576774</v>
+        <v>94422.09484959475</v>
       </c>
       <c r="E5">
-        <v>0.005108022258887793</v>
+        <v>0.006232861936331147</v>
       </c>
       <c r="F5">
-        <v>0.6898398724708215</v>
+        <v>0.6905296766388008</v>
       </c>
       <c r="G5">
-        <v>1.360655737704918</v>
+        <v>1.450819672131147</v>
       </c>
       <c r="H5">
-        <v>0.1197277360460728</v>
+        <v>0.1197452439229522</v>
       </c>
       <c r="I5">
-        <v>0.005068407368045264</v>
+        <v>0.007000253939454762</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -575,25 +575,25 @@
         <v>943</v>
       </c>
       <c r="C6">
-        <v>13361890.28490731</v>
+        <v>13359135.74845482</v>
       </c>
       <c r="D6">
-        <v>138201.7092190425</v>
+        <v>49329.10970550036</v>
       </c>
       <c r="E6">
-        <v>0.009020761208613131</v>
+        <v>0.003953842396188018</v>
       </c>
       <c r="F6">
-        <v>0.6909876265486031</v>
+        <v>0.6922683380702455</v>
       </c>
       <c r="G6">
-        <v>1.542948038176034</v>
+        <v>1.250265111346766</v>
       </c>
       <c r="H6">
-        <v>0.1186097927973194</v>
+        <v>0.1185978453940032</v>
       </c>
       <c r="I6">
-        <v>0.01034297590178134</v>
+        <v>0.003692537499007449</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -604,25 +604,25 @@
         <v>890</v>
       </c>
       <c r="C7">
-        <v>12753198.85762022</v>
+        <v>12752907.34577825</v>
       </c>
       <c r="D7">
-        <v>119373.1685739635</v>
+        <v>34882.611540844</v>
       </c>
       <c r="E7">
-        <v>0.008200570620167135</v>
+        <v>0.003022402970105342</v>
       </c>
       <c r="F7">
-        <v>0.6916452876859673</v>
+        <v>0.6909440643754788</v>
       </c>
       <c r="G7">
-        <v>1.560674157303371</v>
+        <v>1.265168539325843</v>
       </c>
       <c r="H7">
-        <v>0.1132066078789718</v>
+        <v>0.1132159566455185</v>
       </c>
       <c r="I7">
-        <v>0.009360253055462731</v>
+        <v>0.00273526738609856</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -633,25 +633,25 @@
         <v>809</v>
       </c>
       <c r="C8">
-        <v>11148101.06103239</v>
+        <v>11147001.19290712</v>
       </c>
       <c r="D8">
-        <v>20420.85603718308</v>
+        <v>49601.3950815514</v>
       </c>
       <c r="E8">
-        <v>0.002118934499878127</v>
+        <v>0.004945577544790887</v>
       </c>
       <c r="F8">
-        <v>0.6894714982691714</v>
+        <v>0.6894165745275845</v>
       </c>
       <c r="G8">
-        <v>1.247218788627936</v>
+        <v>1.316440049443758</v>
       </c>
       <c r="H8">
-        <v>0.09895860007368718</v>
+        <v>0.09895927019351372</v>
       </c>
       <c r="I8">
-        <v>0.001831778876544556</v>
+        <v>0.004449752379421378</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/sector_summary.xlsx
+++ b/data/outputs/sector_summary.xlsx
@@ -462,7 +462,7 @@
         <v>27612128.92570351</v>
       </c>
       <c r="D2">
-        <v>46690.29756361964</v>
+        <v>54305.71518045494</v>
       </c>
       <c r="E2">
         <v>0.001713220526860417</v>
@@ -471,13 +471,13 @@
         <v>0.6893616691836554</v>
       </c>
       <c r="G2">
-        <v>1.269269776876268</v>
+        <v>1.308316430020284</v>
       </c>
       <c r="H2">
         <v>0.2451310518128871</v>
       </c>
       <c r="I2">
-        <v>0.001690934360376562</v>
+        <v>0.001966734087276515</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -491,7 +491,7 @@
         <v>17738299.12155825</v>
       </c>
       <c r="D3">
-        <v>94367.40951191924</v>
+        <v>101660.7505560984</v>
       </c>
       <c r="E3">
         <v>0.004872875091881172</v>
@@ -500,13 +500,13 @@
         <v>0.6900363533654161</v>
       </c>
       <c r="G3">
-        <v>1.280881195908733</v>
+        <v>1.265932336742722</v>
       </c>
       <c r="H3">
         <v>0.1574745624554699</v>
       </c>
       <c r="I3">
-        <v>0.005319980730127037</v>
+        <v>0.0057311442241125</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -520,7 +520,7 @@
         <v>16544460.35796101</v>
       </c>
       <c r="D4">
-        <v>59192.10363793441</v>
+        <v>66660.95808633778</v>
       </c>
       <c r="E4">
         <v>0.003794104472979617</v>
@@ -529,13 +529,13 @@
         <v>0.687074752583591</v>
       </c>
       <c r="G4">
-        <v>1.287093942054434</v>
+        <v>1.294117647058824</v>
       </c>
       <c r="H4">
         <v>0.1468760695756554</v>
       </c>
       <c r="I4">
-        <v>0.003577759706707618</v>
+        <v>0.004029201112882552</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -549,7 +549,7 @@
         <v>13488381.37391186</v>
       </c>
       <c r="D5">
-        <v>94422.09484959475</v>
+        <v>95684.50570900874</v>
       </c>
       <c r="E5">
         <v>0.006232861936331147</v>
@@ -558,13 +558,13 @@
         <v>0.6905296766388008</v>
       </c>
       <c r="G5">
-        <v>1.450819672131147</v>
+        <v>1.29405737704918</v>
       </c>
       <c r="H5">
         <v>0.1197452439229522</v>
       </c>
       <c r="I5">
-        <v>0.007000253939454762</v>
+        <v>0.007093846404289396</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -578,7 +578,7 @@
         <v>13359135.74845482</v>
       </c>
       <c r="D6">
-        <v>49329.10970550036</v>
+        <v>56299.62294217812</v>
       </c>
       <c r="E6">
         <v>0.003953842396188018</v>
@@ -587,13 +587,13 @@
         <v>0.6922683380702455</v>
       </c>
       <c r="G6">
-        <v>1.250265111346766</v>
+        <v>1.277836691410392</v>
       </c>
       <c r="H6">
         <v>0.1185978453940032</v>
       </c>
       <c r="I6">
-        <v>0.003692537499007449</v>
+        <v>0.004214316255352821</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -607,7 +607,7 @@
         <v>12752907.34577825</v>
       </c>
       <c r="D7">
-        <v>34882.611540844</v>
+        <v>39793.7704862884</v>
       </c>
       <c r="E7">
         <v>0.003022402970105342</v>
@@ -616,13 +616,13 @@
         <v>0.6909440643754788</v>
       </c>
       <c r="G7">
-        <v>1.265168539325843</v>
+        <v>1.29438202247191</v>
       </c>
       <c r="H7">
         <v>0.1132159566455185</v>
       </c>
       <c r="I7">
-        <v>0.00273526738609856</v>
+        <v>0.003120368509496136</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -636,7 +636,7 @@
         <v>11147001.19290712</v>
       </c>
       <c r="D8">
-        <v>49601.3950815514</v>
+        <v>53082.42027069654</v>
       </c>
       <c r="E8">
         <v>0.004945577544790887</v>
@@ -645,13 +645,13 @@
         <v>0.6894165745275845</v>
       </c>
       <c r="G8">
-        <v>1.316440049443758</v>
+        <v>1.273176761433869</v>
       </c>
       <c r="H8">
         <v>0.09895927019351372</v>
       </c>
       <c r="I8">
-        <v>0.004449752379421378</v>
+        <v>0.004762035937026102</v>
       </c>
     </row>
   </sheetData>
